--- a/extenbooks/S1602_extenbook.xlsx
+++ b/extenbooks/S1602_extenbook.xlsx
@@ -9776,7 +9776,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -11194,11 +11194,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11221,76 +11221,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hourly Real Wages and Productivity, US Business Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension_deferred", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1602_research.json", "adequacy_report": "Technical/docs/chapters/CH16_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1602_DPR.md", "epr": "Technical/docs/series/S1602_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1602_load.py", "processor": "Technical/code/P02_processors/P02_S1602_construct.py", "validator": "Technical/code/V03_validators/V03_S1602_validate.py", "processed": "Technical/data/processed/S1602.parquet", "chopped_csv": "Technical/chopped/S1602.csv", "extenbook_xlsx": "Technical/extenbooks/S1602_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:17:23.977169+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1602_extenbook.xlsx
+++ b/extenbooks/S1602_extenbook.xlsx
@@ -9723,7 +9723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A172"/>
+  <dimension ref="A1:A175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -9820,7 +9820,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>**S1602** is the annual co-evolution of hourly **productivity** and hourly **real compensation** in the US Nonfarm Business Sector, 1947-2024, **indexed to 1982 = 100**, plus a Shaikh-original **counterfactual real-compensation path (`ec_c`)** estimated from OLS regression of `ln(ec) ~ ln(y) + time` over the "golden age" 1960-1981 and projected forward. The chart appears as **Figure 16.3** ("Hourly Productivity and Hourly Real Compensation, US Business Sector, 1947-2008") and shows the post-Reagan-era divergence between productivity growth and real-wage growth.</t>
+          <t>**S1602** is the annual co-evolution of hourly **productivity** and hourly **real compensation** in the US Nonfarm Business Sector, 1947-2024, **indexed to 1982 = 100**, plus a Shaikh-original **counterfactual real-compensation path (`ec_c`)** estimated from OLS regression of `ln(ec) ~ ln(y) + time` over the "golden age" 1960-1981 and projected forward. The chart appears as **Figure 16.3** ("Hourly Real Wages and Productivity, US Business Sector, 1947–2012 (1982 = 100)"; the in-text description at p.730 phrases it as the relation between hourly productivity and hourly real compensation "from 1947 to 2008") and shows the post-Reagan-era divergence between productivity growth and real-wage growth.</t>
         </is>
       </c>
     </row>
@@ -9860,230 +9860,226 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+          <t>The shipped chopped carries **five book-period subseries (A, B, C, G, H — all 1947-2012, all sourced from `SHAIKH_APPENDIX_16_2`)**:</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>| **S1602-A** | 1947-2012 | BLS PRS84006153 (Output per hour, Nonfarm Business) via Appendix 16.2 | index 1982=100 (book), originally 1992=100 | Salvaged xlsx |</t>
+          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>| **S1602-B** | 1947-2012 | BLS PRS84006093 (Real Hourly Compensation, Nonfarm Business, CPI-U-RS deflated) via Appendix 16.2 | index 1982=100 (book) | Salvaged xlsx |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>| **S1602-C** | 1947-2012 | Shaikh counterfactual `ec_c` = `Adj Real Hrly EC` from Appendix 16.2 | index 1982=100 | Salvaged xlsx |</t>
+          <t>| **S1602-A** | 1947-2012 | BLS PRS84006153 (Output per hour, Nonfarm Business) via Appendix 16.2 | index 1982=100 (book), originally 1992=100 | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>| **S1602-D** | 2013-2024 | FRED `OPHNFB` (Output per hour, Nonfarm Business) extension | index 2017=100 | FRED API |</t>
+          <t>| **S1602-B** | 1947-2012 | BLS PRS84006093 (Real Hourly Compensation, Nonfarm Business, CPI-U-RS deflated) via Appendix 16.2 | index 1982=100 (book) | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| **S1602-E** | 2013-2024 | FRED `COMPRNFB` (Real Hourly Compensation, Nonfarm Business) extension | index 2017=100 | FRED API |</t>
+          <t>| **S1602-C** | 1947-2012 | Shaikh counterfactual `ec_c` = `Adj Real Hrly EC` from Appendix 16.2 | index 1982=100 | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| **S1602-F** | 2013-2024 | Re-derived `ec_c` extension using forecast from 1960-1981 regression | index 1982=100 | Computed |</t>
+          <t>| **S1602-G** | 1947-2012 | Productivity re-based to **1958=100** (S095-C cross-chapter cadence), from Appendix 16.2 | index 1958=100 | Salvaged xlsx |</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>| **S1602-H** | 1947-2012 | Real Hourly EC re-based to **1958=100** (S095-D cross-chapter cadence), from Appendix 16.2 | index 1958=100 | Salvaged xlsx |</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>**Extensions deferred to Phase 6 (NOT shipped).** The FRED `OPHNFB` (Output per hour), FRED `COMPRNFB` (Real Hourly Compensation), and re-derived counterfactual `ec_c` forecast that would carry S1602 to 2024 are declared in the registry as `extension_deferred_to_phase6: true` and are **absent from the shipped chopped** (book-period 1947-2012 only). An earlier draft of this DPR lettered those three extensions as S1602-D/-E/-F; the shipped chopped instead uses D/E/F-free lettering and adds the 1958=100 rebases at G/H. The deferred extension sources are documented in the EPR, not lettered here. (Corrected 2026-07-02, campaign DF-2.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>**Deflator decision (Phase 4 ratified)**: CPI-U-RS is the canonical Shaikh-consistent deflator (matches BLS PRS84006093 published default at the time the book went to press). PCE deflator is documented as a sensitivity variant in the EPR but not the canonical series.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>## 4. Construction</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S1602 is **composite**. Book period uses Shaikh's distributed Appendix 16.2 values directly (no re-derivation). Extension period re-fetches BLS via FRED at 2017=100 base, rebases to 1982=100 using overlap arithmetic at the splice year 2012, and re-runs the counterfactual regression forecast.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>**Counterfactual regression** (replicated explicitly per Phase 4 Q4):</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>S1602 is **composite**. The shipped chopped uses Shaikh's distributed Appendix 16.2 values directly (no re-derivation), emitting the 1982=100 book series (A/B/C) plus the 1958=100 cross-chapter-cadence rebases (G/H). The Phase-6 extension procedure — re-fetch BLS via FRED at 2017=100 base, rebase to 1982=100 using overlap arithmetic at the splice year 2012, and re-run the counterfactual regression forecast — is **deferred** and not present in the shipped chopped (see §3).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>window:           1960-1981 (Shaikh's "golden age")</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>specification:    ln(ec_t) = alpha + beta * ln(y_t) + gamma * t</t>
+          <t>**Counterfactual regression** (replicated explicitly per Phase 4 Q4):</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fit:              OLS; gamma typically not statistically significant</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>forecast:         ec_c_t = exp( alpha_hat + beta_hat * ln(y_t) + gamma_hat * t )</t>
+          <t>window:           1960-1981 (Shaikh's "golden age")</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  for t = 1982, 1983, ..., 2024</t>
+          <t>specification:    ln(ec_t) = alpha + beta * ln(y_t) + gamma * t</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pre-1982:         ec_c_t = ec_t (identity); counterfactual binds at 1982 by construction</t>
+          <t>fit:              OLS; gamma typically not statistically significant</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>forecast:         ec_c_t = exp( alpha_hat + beta_hat * ln(y_t) + gamma_hat * t )</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  for t = 1982, 1983, ..., 2024</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>pre-1982:         ec_c_t = ec_t (identity); counterfactual binds at 1982 by construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>The regression coefficients are emitted as a sidecar JSON for replication audit.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>- **Book period**: 1947-2012 (66 obs per subseries)</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>- **Extension period**: 2013-2024 (12 obs)</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>- **Total**: 1947-2024</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>- **Gaps**: none</t>
+          <t>- **Book period**: 1947-2012 (66 obs per subseries; A, B, C, G, H each 66 obs)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>- **Extension period**: deferred to Phase 6 (2013-2024 FRED splices + counterfactual re-forecast not yet shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Total shipped**: 1947-2012</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>- **Gaps**: none</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>- **S1602 (final)**: index, 1982 = 100 (matches Fig 16.3 axis)</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- Sub-index variants (`Productivity 1958=100`, etc.) preserved in raw parquet for cross-chapter cadence consistency (S095-C/D in CD2 used 1958=100).</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -10093,421 +10089,421 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>- **S1602 (final)**: index, 1982 = 100 (matches Fig 16.3 axis)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>- Sub-index variants (`Productivity 1958=100`, etc.) preserved in raw parquet for cross-chapter cadence consistency (S095-C/D in CD2 used 1958=100).</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>1. **bls.org typo in book footnote**. The Appendix 16.1 footnote on p. 898 says `http://www.bls.org` — a typo for `http://www.bls.gov`. RSCD canonicalises bls.gov throughout.</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2. **BLS rebase 2012 -&gt; 2017**. BLS rebased PRS84006xxx indices to 2017=100 in 2022. The extension rebases back to 1982=100 via overlap at 2012 (last full Appendix 16.2 year). Pre/post-2012 splice continuity is validated.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>3. **Productivity revisions**. BLS revises productivity quarterly; minor level shifts at the splice are expected and absorbed by the overlap-anchor reindex.</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4. **Counterfactual specification choice**. The regression `ln(ec) ~ ln(y) + time` is Shaikh's published spec. The time coefficient is rarely significant, but is retained to match his Stata code; documented as a methodological choice, not a proxy.</t>
+          <t>1. **bls.org typo in book footnote**. The Appendix 16.1 footnote on p. 898 says `http://www.bls.org` — a typo for `http://www.bls.gov`. RSCD canonicalises bls.gov throughout.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5. **No proxies**. PRS84006093 / PRS84006153 are reachable via FRED COMPRNFB / OPHNFB and via direct data.bls.gov endpoints. The Phase 4 URL substitutions are routing changes, not concept changes.</t>
+          <t>2. **BLS rebase 2012 -&gt; 2017**. BLS rebased PRS84006xxx indices to 2017=100 in 2022. The extension rebases back to 1982=100 via overlap at 2012 (last full Appendix 16.2 year). Pre/post-2012 splice continuity is validated.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3. **Productivity revisions**. BLS revises productivity quarterly; minor level shifts at the splice are expected and absorbed by the overlap-anchor reindex.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>4. **Counterfactual specification choice**. The regression `ln(ec) ~ ln(y) + time` is Shaikh's published spec. The time coefficient is rarely significant, but is retained to match his Stata code; documented as a methodological choice, not a proxy.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5. **No proxies**. PRS84006093 / PRS84006153 are reachable via FRED COMPRNFB / OPHNFB and via direct data.bls.gov endpoints. The Phase 4 URL substitutions are routing changes, not concept changes.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>- **CD legacy ID**: `S095`</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: `S095` (4 subseries A-D)</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S095_*`</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 16, pp. 730-731 (Fig 16.3); Appendix 16.1 p. 898; Appendix 16.2 data</t>
+          <t>- **CD legacy ID**: `S095`</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>- **Downstream dependency**: S1604 `rcorpalt` subseries consumes `ec_c` from S1602 — Phase 5 ordering enforced</t>
+          <t>- **CD2 legacy ID**: `S095` (4 subseries A-D)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S095_*`</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 16, pp. 730-731 (Fig 16.3); Appendix 16.1 p. 898; Appendix 16.2 data</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- **Downstream dependency**: S1604 `rcorpalt` subseries consumes `ec_c` from S1602 — Phase 5 ordering enforced</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>- **Tolerance**: ±1.0% per year on S1602-A and S1602-B against Appendix 16.2 columns `Productivity 1982=100` and `Real Hrly EC 1982=100` for 1947-2012.</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: ±1.0% per year on S1602-A and S1602-B against Appendix 16.2 columns `Productivity 1982=100` and `Real Hrly EC 1982=100` for 1947-2012.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>- **Counterfactual replication**: regress `ln(ec) ~ ln(y) + time` over 1960-1981; coefficients should match Shaikh's published `realecf` column at the 0.01 level when re-multiplied back into level form.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>- **Splice continuity at 2012**: FRED-extension value must match book value within ±1% at the splice year.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="4">
+    <row r="90">
+      <c r="A90" s="4">
         <f>== EPR: S1602_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t># S1602 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>**Series**: S1602 — Hourly Real Wages and Productivity</t>
-        </is>
-      </c>
-    </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t># S1602 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `composite`</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>**Extension method**: re-fetch BLS components via FRED (OPHNFB, COMPRNFB), rebase 2017=100 -&gt; 1982=100 via overlap at 2012, re-run counterfactual regression forecast</t>
+          <t>**Series**: S1602 — Hourly Real Wages and Productivity</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch16-fanout</t>
+          <t>**Construction classification**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>**Extension method**: re-fetch BLS components via FRED (OPHNFB, COMPRNFB), rebase 2017=100 -&gt; 1982=100 via overlap at 2012, re-run counterfactual regression forecast</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>**Author**: opus-subagent-ch16-fanout</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>`time_series`. BLS Major Sector Productivity and Costs is published quarterly without interruption since 1947; FRED republishes the same BLS series as `OPHNFB` and `COMPRNFB`. The counterfactual `ec_c` is a deterministic OLS forecast and recomputes on every extension using only the 1960-1981 fit window.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>## 2. Construction classification</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>`composite` — three subseries (productivity, real compensation, counterfactual) plus their extensions. The counterfactual is a `formula`-style derivation (OLS forecast), so the extension MUST re-run the formula on extended `y` (productivity), per the Anu no-lazy-splice rule for derived quantities.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>## 3. Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-    </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INPUTS</t>
+          <t>## 3. Method</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Appendix 16.2 chopped table:</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">    y_t  = Productivity 1982=100               (1947-2012)</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ec_t = Real Hrly EC 1982=100               (1947-2012)</t>
+          <t>INPUTS</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ec_c_t (Adj Real Hrly EC, book truth)      (1947-2012)</t>
+          <t xml:space="preserve">  Appendix 16.2 chopped table:</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    y_t  = Productivity 1982=100               (1947-2012)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FRED extension:</t>
+          <t xml:space="preserve">    ec_t = Real Hrly EC 1982=100               (1947-2012)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">    OPHNFB    (Output per hour, NFB)           2017=100   monthly -&gt; annual avg</t>
+          <t xml:space="preserve">    ec_c_t (Adj Real Hrly EC, book truth)      (1947-2012)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    COMPRNFB  (Real Hourly Compensation, NFB)  2017=100   monthly -&gt; annual avg</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FRED extension:</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REBASE TO 1982=100</t>
+          <t xml:space="preserve">    OPHNFB    (Output per hour, NFB)           2017=100   monthly -&gt; annual avg</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scale_y  = book_y[2012]  / fred_OPHNFB[2012]</t>
+          <t xml:space="preserve">    COMPRNFB  (Real Hourly Compensation, NFB)  2017=100   monthly -&gt; annual avg</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  scale_ec = book_ec[2012] / fred_COMPRNFB[2012]</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">  y_ext_t  = fred_OPHNFB_t  * scale_y      for t in [2013, 2024]</t>
+          <t>REBASE TO 1982=100</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ec_ext_t = fred_COMPRNFB_t * scale_ec    for t in [2013, 2024]</t>
+          <t xml:space="preserve">  scale_y  = book_y[2012]  / fred_OPHNFB[2012]</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  scale_ec = book_ec[2012] / fred_COMPRNFB[2012]</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>COUNTERFACTUAL REGRESSION (replicates Shaikh's spec)</t>
+          <t xml:space="preserve">  y_ext_t  = fred_OPHNFB_t  * scale_y      for t in [2013, 2024]</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fit window:  1960-1981</t>
+          <t xml:space="preserve">  ec_ext_t = fred_COMPRNFB_t * scale_ec    for t in [2013, 2024]</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  model:       ln(ec_t) = alpha + beta*ln(y_t) + gamma*t</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">  estimate:    OLS  -&gt; (alpha_hat, beta_hat, gamma_hat)</t>
+          <t>COUNTERFACTUAL REGRESSION (replicates Shaikh's spec)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">  forecast:    ec_c_extended_t = exp(alpha_hat + beta_hat*ln(y_t_full) + gamma_hat*t)</t>
+          <t xml:space="preserve">  fit window:  1960-1981</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">               for t in [1982, 2024]</t>
+          <t xml:space="preserve">  model:       ln(ec_t) = alpha + beta*ln(y_t) + gamma*t</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">  pre-1982:    ec_c_extended_t = ec_t  (identity)</t>
+          <t xml:space="preserve">  estimate:    OLS  -&gt; (alpha_hat, beta_hat, gamma_hat)</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  forecast:    ec_c_extended_t = exp(alpha_hat + beta_hat*ln(y_t_full) + gamma_hat*t)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sidecar JSON: Technical/data/processed/_sidecars/S1602_counterfactual_fit.json</t>
+          <t xml:space="preserve">               for t in [1982, 2024]</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">    with {alpha, beta, gamma, se_alpha, se_beta, se_gamma, r2, n}</t>
+          <t xml:space="preserve">  pre-1982:    ec_c_extended_t = ec_t  (identity)</t>
         </is>
       </c>
     </row>
@@ -10517,202 +10513,219 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OUTPUT</t>
+          <t xml:space="preserve">  Sidecar JSON: Technical/data/processed/_sidecars/S1602_counterfactual_fit.json</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1602-A_extended : y_t        for 1947-2024 (book 1947-2012, FRED 2013-2024)</t>
+          <t xml:space="preserve">    with {alpha, beta, gamma, se_alpha, se_beta, se_gamma, r2, n}</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S1602-B_extended : ec_t       for 1947-2024</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1602-C_extended : ec_c_t     for 1947-2024 (re-fit forecast)</t>
+          <t>OUTPUT</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  S1602-A_extended : y_t        for 1947-2024 (book 1947-2012, FRED 2013-2024)</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S1602-B_extended : ec_t       for 1947-2024</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t xml:space="preserve">  S1602-C_extended : ec_c_t     for 1947-2024 (re-fit forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>## 4. Component re-fetching</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Extension re-fetches `OPHNFB` and `COMPRNFB` from FRED each run (TTL 30 days). The counterfactual is recomputed from the re-fit window — never carried forward as a precomputed level. This matches the Anu rule that formula-type series must recompute, not lazy-splice.</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>## 5. Proxies</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>**None.** PRS84006093 / PRS84006153 are the BLS source IDs cited in the book; FRED `COMPRNFB` and `OPHNFB` are the public-domain redistributions of those exact BLS series, no concept substitution. The book footnote URL `bls.org` is a documented typo for `bls.gov`.</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>## 6. Synthetic data</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>**None permitted.** If FRED returns NaN at the 2012 overlap, the loader walks back to the next available year. If no overlap in 2010-2012, the extension fails hard with `extension_status: no_overlap` rather than silently splicing.</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>## 7. Failure modes &amp; graceful degradation</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr"/>
-    </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>| Failure | Detection | Action |</t>
-        </is>
-      </c>
+      <c r="A157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>## 7. Failure modes &amp; graceful degradation</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>| `FRED_API_KEY` missing | startup | Loader skips extension; baseline 1947-2012 published only |</t>
-        </is>
-      </c>
+      <c r="A159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>| FRED returns 5xx | retry 3× w/ backoff | If still failing, mark extension `data_unavailable` |</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>| Overlap NaN at 2012 | processor | Walk back 2011, 2010; if none, FAIL |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>| Counterfactual non-convergence | OLS exception | Emit sidecar JSON with `converged: false`; baseline `ec_c` (book truth) remains valid |</t>
+          <t>| `FRED_API_KEY` missing | startup | Loader skips extension; baseline 1947-2012 published only |</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>| BLS rebases again post-2017 | next-run cache | Reindex factor recomputed from latest overlap; base-year-invariant |</t>
+          <t>| FRED returns 5xx | retry 3× w/ backoff | If still failing, mark extension `data_unavailable` |</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>| Overlap NaN at 2012 | processor | Walk back 2011, 2010; if none, FAIL |</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>| Counterfactual non-convergence | OLS exception | Emit sidecar JSON with `converged: false`; baseline `ec_c` (book truth) remains valid |</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>| BLS rebases again post-2017 | next-run cache | Reindex factor recomputed from latest overlap; base-year-invariant |</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>## 8. CD2 divergence</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>CD2's `S095` decomposed into 4 subseries (A productivity 1982=100, B real comp 1982=100, C productivity 1958=100, D real comp 1958=100). RSCD S1602 retains A and B as canonical (matching Fig 16.3 axis) and treats the 1958=100 rebases as derived variants computed on demand. The counterfactual `ec_c` is promoted to a first-class subseries (S1602-C) since Ch16 explicitly depends on it.</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>## 9. Sensitivity variants</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr"/>
-    </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>- **PCE deflator alternative**: If a user prefers PCE-deflated real compensation (rather than CPI-U-RS), a sensitivity variant can be computed using FRED `COMPRNFB` over PCEPI (or BLS PCE-deflated PRS84006153). Documented but not the canonical series.</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
+        <is>
+          <t>## 9. Sensitivity variants</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>- **PCE deflator alternative**: If a user prefers PCE-deflated real compensation (rather than CPI-U-RS), a sensitivity variant can be computed using FRED `COMPRNFB` over PCEPI (or BLS PCE-deflated PRS84006153). Documented but not the canonical series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>- **Time-trend coefficient**: The `gamma` (time-trend in the counterfactual regression) is included even though typically non-significant; users wanting Shaikh's published "stripped" form can set gamma=0 via a config flag.</t>
         </is>
@@ -11179,7 +11192,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-19T00:19:56.062690+00:00</t>
+          <t>2026-07-02T06:20:05.622933+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1602_extenbook.xlsx
+++ b/extenbooks/S1602_extenbook.xlsx
@@ -11192,7 +11192,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:05.622933+00:00</t>
+          <t>2026-07-11T03:44:23.652711+00:00</t>
         </is>
       </c>
     </row>
@@ -11207,11 +11207,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11234,6 +11234,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_16_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "fix-completed-then-publish", "reason": "KB-verified against figure 16.3 and appendix; registry name correct. DPR figure-caption corrected to the KB caption (was the in-text 1947\u20132008 phrasing). Verbatim quotes confirmed.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1602_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1602_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cross-series dependency: S1604 rcorpalt consumes S1602 ec_c; Phase 5 ingestion order S1602 -&gt; S1604.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>index_1982=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
